--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260703.xlsx
@@ -623,17 +623,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>441,249,976</t>
+          <t>168,878,799</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -645,17 +645,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>168,878,799</t>
+          <t>441,249,976</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
